--- a/models/mapany/mapany_results.xlsx
+++ b/models/mapany/mapany_results.xlsx
@@ -6432,76 +6432,76 @@
         <v>3</v>
       </c>
       <c r="M40">
-        <v>3.4072263160005605</v>
+        <v>3.307971440000074</v>
       </c>
       <c r="N40">
-        <v>23.899341437000658</v>
+        <v>21.266299063999895</v>
       </c>
       <c r="O40">
-        <v>4.335254645000532</v>
+        <v>3.982978941000056</v>
       </c>
       <c r="P40">
-        <v>12.958304223000596</v>
+        <v>11.902213237999831</v>
       </c>
       <c r="Q40">
-        <v>40.57916961200044</v>
+        <v>36.79326079200018</v>
       </c>
       <c r="R40">
-        <v>2.9831780580007035</v>
+        <v>2.639655237999932</v>
       </c>
       <c r="S40">
-        <v>2.094556633999673</v>
+        <v>2.092951557999868</v>
       </c>
       <c r="T40">
-        <v>3.3791448759993727</v>
+        <v>2.6681641970001237</v>
       </c>
       <c r="U40">
-        <v>1.118326722999882</v>
+        <v>1.1718396860001121</v>
       </c>
       <c r="V40">
-        <v>1.1122640849998788</v>
+        <v>1.1077317550000316</v>
       </c>
       <c r="W40">
-        <v>1.4360350610004389</v>
+        <v>1.4163376659998903</v>
       </c>
       <c r="X40">
-        <v>0.006588530000044557</v>
+        <v>0.0074370160000398755</v>
       </c>
       <c r="Y40">
-        <v>0.006586819999938598</v>
+        <v>0.00668531500014069</v>
       </c>
       <c r="Z40">
-        <v>0.009333527000308095</v>
+        <v>0.008492400000022826</v>
       </c>
       <c r="AA40">
-        <v>0.22960222999972757</v>
+        <v>0.2286184490001233</v>
       </c>
       <c r="AB40">
-        <v>0.22686583799986693</v>
+        <v>0.21204573199997867</v>
       </c>
       <c r="AC40">
-        <v>0.24405510900032823</v>
+        <v>0.23167665100004342</v>
       </c>
       <c r="AD40">
-        <v>3.7843096469996453</v>
+        <v>3.748794142999941</v>
       </c>
       <c r="AE40">
-        <v>4.727976447000401</v>
+        <v>4.060844958999951</v>
       </c>
       <c r="AF40">
-        <v>9954.625</v>
+        <v>10044.40625</v>
       </c>
       <c r="AG40">
-        <v>3001.984375</v>
+        <v>3026.8359375</v>
       </c>
       <c r="AH40">
-        <v>2321.8671875</v>
+        <v>2346.74609375</v>
       </c>
       <c r="AI40">
-        <v>3003.0</v>
+        <v>3043.8359375</v>
       </c>
       <c r="AJ40">
-        <v>10316.375</v>
+        <v>10325.171875</v>
       </c>
       <c r="AK40">
         <v>4686.337890625</v>
@@ -11997,76 +11997,76 @@
         <v>3</v>
       </c>
       <c r="M75">
-        <v>3.641375329999846</v>
+        <v>3.2109392880001906</v>
       </c>
       <c r="N75">
-        <v>24.069986712999935</v>
+        <v>23.373810952999975</v>
       </c>
       <c r="O75">
-        <v>1.884098978000111</v>
+        <v>1.9343158589999803</v>
       </c>
       <c r="P75">
-        <v>5.929331032999926</v>
+        <v>5.793640889000017</v>
       </c>
       <c r="Q75">
-        <v>33.98342203399989</v>
+        <v>32.73350293400017</v>
       </c>
       <c r="R75">
-        <v>1.3527699829999165</v>
+        <v>1.265557254999976</v>
       </c>
       <c r="S75">
-        <v>1.0086706699999013</v>
+        <v>1.0494415210000625</v>
       </c>
       <c r="T75">
-        <v>1.4198056280001765</v>
+        <v>1.2788148170000113</v>
       </c>
       <c r="U75">
-        <v>0.610484366000037</v>
+        <v>0.6021564359998592</v>
       </c>
       <c r="V75">
-        <v>0.4410810260001199</v>
+        <v>0.45371649799994884</v>
       </c>
       <c r="W75">
-        <v>0.7325575760000902</v>
+        <v>0.7893053489999602</v>
       </c>
       <c r="X75">
-        <v>0.004180121999979747</v>
+        <v>0.004161021000072651</v>
       </c>
       <c r="Y75">
-        <v>0.004069135000008828</v>
+        <v>0.0041226669998195575</v>
       </c>
       <c r="Z75">
-        <v>0.004218311000158792</v>
+        <v>0.004939340999953856</v>
       </c>
       <c r="AA75">
-        <v>0.08822660900000301</v>
+        <v>0.07639875700010634</v>
       </c>
       <c r="AB75">
-        <v>0.08578438100016683</v>
+        <v>0.07483206200004133</v>
       </c>
       <c r="AC75">
-        <v>0.089427705999924</v>
+        <v>0.09016711499998564</v>
       </c>
       <c r="AD75">
-        <v>1.8350144040000487</v>
+        <v>1.8001311509999596</v>
       </c>
       <c r="AE75">
-        <v>2.1230039189999843</v>
+        <v>1.9601971879999383</v>
       </c>
       <c r="AF75">
-        <v>10021.24609375</v>
+        <v>10124.140625</v>
       </c>
       <c r="AG75">
-        <v>2603.6640625</v>
+        <v>2616.87109375</v>
       </c>
       <c r="AH75">
-        <v>2324.33984375</v>
+        <v>2336.62109375</v>
       </c>
       <c r="AI75">
-        <v>2625.78515625</v>
+        <v>2642.3359375</v>
       </c>
       <c r="AJ75">
-        <v>10316.74609375</v>
+        <v>10326.05859375</v>
       </c>
       <c r="AK75">
         <v>4686.337890625</v>
@@ -12792,76 +12792,76 @@
         <v>3</v>
       </c>
       <c r="M80">
-        <v>3.4205086590000064</v>
+        <v>3.3758050020001065</v>
       </c>
       <c r="N80">
-        <v>24.472596734000035</v>
+        <v>21.783002313999987</v>
       </c>
       <c r="O80">
-        <v>4.5470065630001955</v>
+        <v>3.959147944000051</v>
       </c>
       <c r="P80">
-        <v>13.478462721999676</v>
+        <v>11.896582155000033</v>
       </c>
       <c r="Q80">
-        <v>41.6913934170002</v>
+        <v>37.38022831299986</v>
       </c>
       <c r="R80">
-        <v>3.1506521029996293</v>
+        <v>2.5828237339999305</v>
       </c>
       <c r="S80">
-        <v>2.1851740960000825</v>
+        <v>2.171831348000069</v>
       </c>
       <c r="T80">
-        <v>3.3468728550001288</v>
+        <v>2.663513019999982</v>
       </c>
       <c r="U80">
-        <v>1.1685364549998667</v>
+        <v>1.1661787040000036</v>
       </c>
       <c r="V80">
-        <v>1.1532885109995732</v>
+        <v>1.1337851400001</v>
       </c>
       <c r="W80">
-        <v>1.6755652399997416</v>
+        <v>1.3839314790000117</v>
       </c>
       <c r="X80">
-        <v>0.007777092000196717</v>
+        <v>0.008589859000039723</v>
       </c>
       <c r="Y80">
-        <v>0.00666918299975805</v>
+        <v>0.008492405999959374</v>
       </c>
       <c r="Z80">
-        <v>0.008804188999874896</v>
+        <v>0.009162328999991587</v>
       </c>
       <c r="AA80">
-        <v>0.21973544599995876</v>
+        <v>0.2200585079999655</v>
       </c>
       <c r="AB80">
-        <v>0.2126959900001566</v>
+        <v>0.20067609100010486</v>
       </c>
       <c r="AC80">
-        <v>0.23097586299991235</v>
+        <v>0.23050876100001005</v>
       </c>
       <c r="AD80">
-        <v>4.100938394999957</v>
+        <v>3.7951886190001005</v>
       </c>
       <c r="AE80">
-        <v>4.719914415000403</v>
+        <v>4.026147540000011</v>
       </c>
       <c r="AF80">
-        <v>10312.27734375</v>
+        <v>10062.39453125</v>
       </c>
       <c r="AG80">
-        <v>3004.08203125</v>
+        <v>2972.87109375</v>
       </c>
       <c r="AH80">
-        <v>2320.7265625</v>
+        <v>2336.04296875</v>
       </c>
       <c r="AI80">
-        <v>3017.703125</v>
+        <v>3013.15625</v>
       </c>
       <c r="AJ80">
-        <v>10316.65234375</v>
+        <v>10325.375</v>
       </c>
       <c r="AK80">
         <v>4686.337890625</v>
@@ -15177,76 +15177,76 @@
         <v>3</v>
       </c>
       <c r="M95">
-        <v>3.358556294999289</v>
+        <v>6.395511046000138</v>
       </c>
       <c r="N95">
-        <v>24.081961512998532</v>
+        <v>27.25791823899999</v>
       </c>
       <c r="O95">
-        <v>1.1022031569991668</v>
+        <v>1.1539303910001308</v>
       </c>
       <c r="P95">
-        <v>3.7360798539993993</v>
+        <v>4.377200949000098</v>
       </c>
       <c r="Q95">
-        <v>31.49537787999725</v>
+        <v>38.36914942900012</v>
       </c>
       <c r="R95">
-        <v>0.6168163069996808</v>
+        <v>0.5799363300000095</v>
       </c>
       <c r="S95">
-        <v>0.6036381710000569</v>
+        <v>0.5675857310000083</v>
       </c>
       <c r="T95">
-        <v>0.6187413600018772</v>
+        <v>0.6113235860000259</v>
       </c>
       <c r="U95">
-        <v>0.3892238450025616</v>
+        <v>0.4832041480001408</v>
       </c>
       <c r="V95">
-        <v>0.38728136400095536</v>
+        <v>0.381479698000021</v>
       </c>
       <c r="W95">
-        <v>0.7309325249989342</v>
+        <v>1.3558999159999985</v>
       </c>
       <c r="X95">
-        <v>0.003768251001019962</v>
+        <v>0.0032183639998493163</v>
       </c>
       <c r="Y95">
-        <v>0.003386014999705367</v>
+        <v>0.0032023039998421154</v>
       </c>
       <c r="Z95">
-        <v>0.004318814997532172</v>
+        <v>0.004314352999926996</v>
       </c>
       <c r="AA95">
-        <v>0.09300639700086322</v>
+        <v>0.0948810989998492</v>
       </c>
       <c r="AB95">
-        <v>0.09249665099923732</v>
+        <v>0.09455907200003821</v>
       </c>
       <c r="AC95">
-        <v>0.09520506999979261</v>
+        <v>0.09965344200008985</v>
       </c>
       <c r="AD95">
-        <v>1.092652209001244</v>
+        <v>1.0597693150000396</v>
       </c>
       <c r="AE95">
-        <v>1.4448355679996894</v>
+        <v>2.066382900999997</v>
       </c>
       <c r="AF95">
-        <v>9953.484375</v>
+        <v>10155.8125</v>
       </c>
       <c r="AG95">
-        <v>2334.72265625</v>
+        <v>2364.890625</v>
       </c>
       <c r="AH95">
-        <v>2325.21875</v>
+        <v>2333.86328125</v>
       </c>
       <c r="AI95">
-        <v>2338.77734375</v>
+        <v>2373.88671875</v>
       </c>
       <c r="AJ95">
-        <v>10316.734375</v>
+        <v>10322.703125</v>
       </c>
       <c r="AK95">
         <v>4686.337890625</v>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/nerf_llff_data/fern/images/scen_1/IMG_4026.JPG</t>
+          <t>/home/kamil/dataset/nerf_llff_data/fern/images/scen_1/IMG_4029.JPG</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -19470,76 +19470,76 @@
         <v>3</v>
       </c>
       <c r="M122">
-        <v>3.388627247999466</v>
+        <v>3.38945016699995</v>
       </c>
       <c r="N122">
-        <v>23.966690232000474</v>
+        <v>23.110532857999942</v>
       </c>
       <c r="O122">
-        <v>0.44623862099979306</v>
+        <v>0.4548805619999712</v>
       </c>
       <c r="P122">
-        <v>1.9119925309996688</v>
+        <v>1.855783246000101</v>
       </c>
       <c r="Q122">
-        <v>29.57838451799944</v>
+        <v>28.658507181999994</v>
       </c>
       <c r="R122">
-        <v>0.1388015920001635</v>
+        <v>0.14208419999999933</v>
       </c>
       <c r="S122">
-        <v>0.13864111800012324</v>
+        <v>0.14053161099991485</v>
       </c>
       <c r="T122">
-        <v>0.16153848900012235</v>
+        <v>0.15165687100011382</v>
       </c>
       <c r="U122">
-        <v>0.2567609320003612</v>
+        <v>0.2659847259999424</v>
       </c>
       <c r="V122">
-        <v>0.2541588269996282</v>
+        <v>0.2605326610000702</v>
       </c>
       <c r="W122">
-        <v>0.7185796600006142</v>
+        <v>0.6483955869998681</v>
       </c>
       <c r="X122">
-        <v>0.0028169099996375735</v>
+        <v>0.0028090020000490767</v>
       </c>
       <c r="Y122">
-        <v>0.00216154000008828</v>
+        <v>0.002284440999801518</v>
       </c>
       <c r="Z122">
-        <v>0.0030182399996192544</v>
+        <v>0.0029868249998799</v>
       </c>
       <c r="AA122">
-        <v>0.04718600699925446</v>
+        <v>0.04508086500004538</v>
       </c>
       <c r="AB122">
-        <v>0.04667398200035677</v>
+        <v>0.0444493649999913</v>
       </c>
       <c r="AC122">
-        <v>0.047407028000634455</v>
+        <v>0.05010945300000458</v>
       </c>
       <c r="AD122">
-        <v>0.4418746960000135</v>
+        <v>0.4496149050000895</v>
       </c>
       <c r="AE122">
-        <v>0.9304272159997709</v>
+        <v>0.8532950299997992</v>
       </c>
       <c r="AF122">
-        <v>10064.0234375</v>
+        <v>10120.78515625</v>
       </c>
       <c r="AG122">
-        <v>2319.5546875</v>
+        <v>2329.48828125</v>
       </c>
       <c r="AH122">
-        <v>2316.7109375</v>
+        <v>2328.49609375</v>
       </c>
       <c r="AI122">
-        <v>2319.625</v>
+        <v>2329.5078125</v>
       </c>
       <c r="AJ122">
-        <v>10317.1484375</v>
+        <v>10325.71484375</v>
       </c>
       <c r="AK122">
         <v>4686.337890625</v>
@@ -31480,28 +31480,28 @@
         <v>1</v>
       </c>
       <c r="G116">
-        <v>2.094556633999673</v>
+        <v>2.092951557999868</v>
       </c>
       <c r="H116">
-        <v>1.4360350610004389</v>
+        <v>1.4163376659998903</v>
       </c>
       <c r="I116">
-        <v>0.009333527000308095</v>
+        <v>0.0074370160000398755</v>
       </c>
       <c r="J116">
-        <v>0.24405510900032823</v>
+        <v>0.23167665100004342</v>
       </c>
       <c r="K116">
-        <v>3.7843096469996453</v>
+        <v>3.748794142999941</v>
       </c>
       <c r="L116">
-        <v>2186.90625</v>
+        <v>2196.921875</v>
       </c>
       <c r="M116">
-        <v>2300.13671875</v>
+        <v>2324.8515625</v>
       </c>
       <c r="N116">
-        <v>2321.8671875</v>
+        <v>2346.74609375</v>
       </c>
       <c r="O116">
         <v>7525.55859375</v>
@@ -31540,28 +31540,28 @@
         <v>2</v>
       </c>
       <c r="G117">
-        <v>3.3791448759993727</v>
+        <v>2.6681641970001237</v>
       </c>
       <c r="H117">
-        <v>1.1122640849998788</v>
+        <v>1.1718396860001121</v>
       </c>
       <c r="I117">
-        <v>0.006586819999938598</v>
+        <v>0.008492400000022826</v>
       </c>
       <c r="J117">
-        <v>0.22960222999972757</v>
+        <v>0.21204573199997867</v>
       </c>
       <c r="K117">
-        <v>4.727976447000401</v>
+        <v>4.060844958999951</v>
       </c>
       <c r="L117">
-        <v>2300.13671875</v>
+        <v>2324.8515625</v>
       </c>
       <c r="M117">
-        <v>2301.109375</v>
+        <v>2325.8515625</v>
       </c>
       <c r="N117">
-        <v>3001.984375</v>
+        <v>3026.8359375</v>
       </c>
       <c r="O117">
         <v>7525.55859375</v>
@@ -31600,28 +31600,28 @@
         <v>3</v>
       </c>
       <c r="G118">
-        <v>2.9831780580007035</v>
+        <v>2.639655237999932</v>
       </c>
       <c r="H118">
-        <v>1.118326722999882</v>
+        <v>1.1077317550000316</v>
       </c>
       <c r="I118">
-        <v>0.006588530000044557</v>
+        <v>0.00668531500014069</v>
       </c>
       <c r="J118">
-        <v>0.22686583799986693</v>
+        <v>0.2286184490001233</v>
       </c>
       <c r="K118">
-        <v>4.335254645000532</v>
+        <v>3.982978941000056</v>
       </c>
       <c r="L118">
-        <v>2301.109375</v>
+        <v>2325.85546875</v>
       </c>
       <c r="M118">
-        <v>2301.15234375</v>
+        <v>2325.87890625</v>
       </c>
       <c r="N118">
-        <v>3003.0</v>
+        <v>3043.8359375</v>
       </c>
       <c r="O118">
         <v>7525.55859375</v>
@@ -37780,28 +37780,28 @@
         <v>1</v>
       </c>
       <c r="G221">
-        <v>1.0086706699999013</v>
+        <v>1.0494415210000625</v>
       </c>
       <c r="H221">
-        <v>0.7325575760000902</v>
+        <v>0.7893053489999602</v>
       </c>
       <c r="I221">
-        <v>0.004069135000008828</v>
+        <v>0.004939340999953856</v>
       </c>
       <c r="J221">
-        <v>0.089427705999924</v>
+        <v>0.09016711499998564</v>
       </c>
       <c r="K221">
-        <v>1.8350144040000487</v>
+        <v>1.9343158589999803</v>
       </c>
       <c r="L221">
-        <v>2187.21484375</v>
+        <v>2197.41015625</v>
       </c>
       <c r="M221">
-        <v>2316.4765625</v>
+        <v>2329.6484375</v>
       </c>
       <c r="N221">
-        <v>2324.33984375</v>
+        <v>2336.62109375</v>
       </c>
       <c r="O221">
         <v>7368.7216796875</v>
@@ -37840,28 +37840,28 @@
         <v>2</v>
       </c>
       <c r="G222">
-        <v>1.4198056280001765</v>
+        <v>1.2788148170000113</v>
       </c>
       <c r="H222">
-        <v>0.610484366000037</v>
+        <v>0.6021564359998592</v>
       </c>
       <c r="I222">
-        <v>0.004218311000158792</v>
+        <v>0.0041226669998195575</v>
       </c>
       <c r="J222">
-        <v>0.08822660900000301</v>
+        <v>0.07483206200004133</v>
       </c>
       <c r="K222">
-        <v>2.1230039189999843</v>
+        <v>1.9601971879999383</v>
       </c>
       <c r="L222">
-        <v>2316.4765625</v>
+        <v>2329.6484375</v>
       </c>
       <c r="M222">
-        <v>2312.9140625</v>
+        <v>2328.4375</v>
       </c>
       <c r="N222">
-        <v>2625.78515625</v>
+        <v>2616.87109375</v>
       </c>
       <c r="O222">
         <v>7368.7216796875</v>
@@ -37900,28 +37900,28 @@
         <v>3</v>
       </c>
       <c r="G223">
-        <v>1.3527699829999165</v>
+        <v>1.265557254999976</v>
       </c>
       <c r="H223">
-        <v>0.4410810260001199</v>
+        <v>0.45371649799994884</v>
       </c>
       <c r="I223">
-        <v>0.004180121999979747</v>
+        <v>0.004161021000072651</v>
       </c>
       <c r="J223">
-        <v>0.08578438100016683</v>
+        <v>0.07639875700010634</v>
       </c>
       <c r="K223">
-        <v>1.884098978000111</v>
+        <v>1.8001311509999596</v>
       </c>
       <c r="L223">
-        <v>2312.9140625</v>
+        <v>2328.44140625</v>
       </c>
       <c r="M223">
-        <v>2312.9140625</v>
+        <v>2328.44140625</v>
       </c>
       <c r="N223">
-        <v>2603.6640625</v>
+        <v>2642.3359375</v>
       </c>
       <c r="O223">
         <v>7368.7216796875</v>
@@ -38680,28 +38680,28 @@
         <v>1</v>
       </c>
       <c r="G236">
-        <v>2.1851740960000825</v>
+        <v>2.171831348000069</v>
       </c>
       <c r="H236">
-        <v>1.6755652399997416</v>
+        <v>1.3839314790000117</v>
       </c>
       <c r="I236">
-        <v>0.008804188999874896</v>
+        <v>0.008589859000039723</v>
       </c>
       <c r="J236">
-        <v>0.23097586299991235</v>
+        <v>0.23050876100001005</v>
       </c>
       <c r="K236">
-        <v>4.100938394999957</v>
+        <v>3.7951886190001005</v>
       </c>
       <c r="L236">
-        <v>2187.12890625</v>
+        <v>2197.19921875</v>
       </c>
       <c r="M236">
-        <v>2299.81640625</v>
+        <v>2315.1328125</v>
       </c>
       <c r="N236">
-        <v>2320.7265625</v>
+        <v>2336.04296875</v>
       </c>
       <c r="O236">
         <v>7525.55859375</v>
@@ -38740,28 +38740,28 @@
         <v>2</v>
       </c>
       <c r="G237">
-        <v>3.3468728550001288</v>
+        <v>2.663513019999982</v>
       </c>
       <c r="H237">
-        <v>1.1532885109995732</v>
+        <v>1.1337851400001</v>
       </c>
       <c r="I237">
-        <v>0.00666918299975805</v>
+        <v>0.008492405999959374</v>
       </c>
       <c r="J237">
-        <v>0.2126959900001566</v>
+        <v>0.2200585079999655</v>
       </c>
       <c r="K237">
-        <v>4.719914415000403</v>
+        <v>4.026147540000011</v>
       </c>
       <c r="L237">
-        <v>2299.81640625</v>
+        <v>2315.1328125</v>
       </c>
       <c r="M237">
-        <v>2300.8203125</v>
+        <v>2316.1328125</v>
       </c>
       <c r="N237">
-        <v>3017.703125</v>
+        <v>2972.87109375</v>
       </c>
       <c r="O237">
         <v>7525.55859375</v>
@@ -38800,28 +38800,28 @@
         <v>3</v>
       </c>
       <c r="G238">
-        <v>3.1506521029996293</v>
+        <v>2.5828237339999305</v>
       </c>
       <c r="H238">
-        <v>1.1685364549998667</v>
+        <v>1.1661787040000036</v>
       </c>
       <c r="I238">
-        <v>0.007777092000196717</v>
+        <v>0.009162328999991587</v>
       </c>
       <c r="J238">
-        <v>0.21973544599995876</v>
+        <v>0.20067609100010486</v>
       </c>
       <c r="K238">
-        <v>4.5470065630001955</v>
+        <v>3.959147944000051</v>
       </c>
       <c r="L238">
-        <v>2300.8203125</v>
+        <v>2316.13671875</v>
       </c>
       <c r="M238">
-        <v>2300.84765625</v>
+        <v>2316.15625</v>
       </c>
       <c r="N238">
-        <v>3004.08203125</v>
+        <v>3013.15625</v>
       </c>
       <c r="O238">
         <v>7525.55859375</v>
@@ -41380,28 +41380,28 @@
         <v>1</v>
       </c>
       <c r="G281">
-        <v>0.6168163069996808</v>
+        <v>0.6113235860000259</v>
       </c>
       <c r="H281">
-        <v>0.7309325249989342</v>
+        <v>1.3558999159999985</v>
       </c>
       <c r="I281">
-        <v>0.003768251001019962</v>
+        <v>0.004314352999926996</v>
       </c>
       <c r="J281">
-        <v>0.09300639700086322</v>
+        <v>0.09455907200003821</v>
       </c>
       <c r="K281">
-        <v>1.4448355679996894</v>
+        <v>2.066382900999997</v>
       </c>
       <c r="L281">
-        <v>2187.09375</v>
+        <v>2194.28515625</v>
       </c>
       <c r="M281">
-        <v>2317.34765625</v>
+        <v>2325.859375</v>
       </c>
       <c r="N281">
-        <v>2325.21875</v>
+        <v>2333.86328125</v>
       </c>
       <c r="O281">
         <v>7295.90869140625</v>
@@ -41440,28 +41440,28 @@
         <v>2</v>
       </c>
       <c r="G282">
-        <v>0.6187413600018772</v>
+        <v>0.5675857310000083</v>
       </c>
       <c r="H282">
-        <v>0.38728136400095536</v>
+        <v>0.4832041480001408</v>
       </c>
       <c r="I282">
-        <v>0.003386014999705367</v>
+        <v>0.0032183639998493163</v>
       </c>
       <c r="J282">
-        <v>0.09249665099923732</v>
+        <v>0.09965344200008985</v>
       </c>
       <c r="K282">
-        <v>1.1022031569991668</v>
+        <v>1.1539303910001308</v>
       </c>
       <c r="L282">
-        <v>2317.34765625</v>
+        <v>2325.859375</v>
       </c>
       <c r="M282">
-        <v>2300.52734375</v>
+        <v>2357.88671875</v>
       </c>
       <c r="N282">
-        <v>2334.72265625</v>
+        <v>2364.890625</v>
       </c>
       <c r="O282">
         <v>7295.90869140625</v>
@@ -41500,28 +41500,28 @@
         <v>3</v>
       </c>
       <c r="G283">
-        <v>0.6036381710000569</v>
+        <v>0.5799363300000095</v>
       </c>
       <c r="H283">
-        <v>0.3892238450025616</v>
+        <v>0.381479698000021</v>
       </c>
       <c r="I283">
-        <v>0.004318814997532172</v>
+        <v>0.0032023039998421154</v>
       </c>
       <c r="J283">
-        <v>0.09520506999979261</v>
+        <v>0.0948810989998492</v>
       </c>
       <c r="K283">
-        <v>1.092652209001244</v>
+        <v>1.0597693150000396</v>
       </c>
       <c r="L283">
-        <v>2300.52734375</v>
+        <v>2357.890625</v>
       </c>
       <c r="M283">
-        <v>2300.53125</v>
+        <v>2310.05078125</v>
       </c>
       <c r="N283">
-        <v>2338.77734375</v>
+        <v>2373.88671875</v>
       </c>
       <c r="O283">
         <v>7295.90869140625</v>
@@ -46240,28 +46240,28 @@
         <v>1</v>
       </c>
       <c r="G362">
-        <v>0.16153848900012235</v>
+        <v>0.15165687100011382</v>
       </c>
       <c r="H362">
-        <v>0.7185796600006142</v>
+        <v>0.6483955869998681</v>
       </c>
       <c r="I362">
-        <v>0.0028169099996375735</v>
+        <v>0.0028090020000490767</v>
       </c>
       <c r="J362">
-        <v>0.04718600699925446</v>
+        <v>0.05010945300000458</v>
       </c>
       <c r="K362">
-        <v>0.9304272159997709</v>
+        <v>0.8532950299997992</v>
       </c>
       <c r="L362">
-        <v>2187.625</v>
+        <v>2197.7109375</v>
       </c>
       <c r="M362">
-        <v>2316.6796875</v>
+        <v>2328.49609375</v>
       </c>
       <c r="N362">
-        <v>2319.625</v>
+        <v>2328.49609375</v>
       </c>
       <c r="O362">
         <v>7290.302734375</v>
@@ -46300,28 +46300,28 @@
         <v>2</v>
       </c>
       <c r="G363">
-        <v>0.13864111800012324</v>
+        <v>0.14053161099991485</v>
       </c>
       <c r="H363">
-        <v>0.2541588269996282</v>
+        <v>0.2659847259999424</v>
       </c>
       <c r="I363">
-        <v>0.00216154000008828</v>
+        <v>0.0029868249998799</v>
       </c>
       <c r="J363">
-        <v>0.04667398200035677</v>
+        <v>0.04508086500004538</v>
       </c>
       <c r="K363">
-        <v>0.4418746960000135</v>
+        <v>0.4548805619999712</v>
       </c>
       <c r="L363">
-        <v>2316.6796875</v>
+        <v>2328.49609375</v>
       </c>
       <c r="M363">
-        <v>2317.671875</v>
+        <v>2329.484375</v>
       </c>
       <c r="N363">
-        <v>2319.5546875</v>
+        <v>2329.48828125</v>
       </c>
       <c r="O363">
         <v>7290.302734375</v>
@@ -46360,28 +46360,28 @@
         <v>3</v>
       </c>
       <c r="G364">
-        <v>0.1388015920001635</v>
+        <v>0.14208419999999933</v>
       </c>
       <c r="H364">
-        <v>0.2567609320003612</v>
+        <v>0.2605326610000702</v>
       </c>
       <c r="I364">
-        <v>0.0030182399996192544</v>
+        <v>0.002284440999801518</v>
       </c>
       <c r="J364">
-        <v>0.047407028000634455</v>
+        <v>0.0444493649999913</v>
       </c>
       <c r="K364">
-        <v>0.44623862099979306</v>
+        <v>0.4496149050000895</v>
       </c>
       <c r="L364">
-        <v>2316.70703125</v>
+        <v>2329.484375</v>
       </c>
       <c r="M364">
-        <v>2316.7109375</v>
+        <v>2329.5078125</v>
       </c>
       <c r="N364">
-        <v>2316.7109375</v>
+        <v>2329.5078125</v>
       </c>
       <c r="O364">
         <v>7290.302734375</v>
@@ -57663,12 +57663,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/custom/mural_king/images/scen_3/IMG_8737.jpg</t>
+          <t>/home/kamil/dataset/custom/mural_king/images/scen_3/IMG_8740.jpg</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>IMG_8737.jpg</t>
+          <t>IMG_8740.jpg</t>
         </is>
       </c>
     </row>
@@ -62943,12 +62943,12 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/custom/synagogue/images/scen_2/IMG_8785.jpg</t>
+          <t>/home/kamil/dataset/custom/synagogue/images/scen_2/IMG_8787.jpg</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>IMG_8785.jpg</t>
+          <t>IMG_8787.jpg</t>
         </is>
       </c>
     </row>
@@ -63703,12 +63703,12 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/custom/tennis_table/images/scen_3/IMG_8862.jpg</t>
+          <t>/home/kamil/dataset/custom/tennis_table/images/scen_3/IMG_8861.jpg</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>IMG_8862.jpg</t>
+          <t>IMG_8861.jpg</t>
         </is>
       </c>
     </row>
@@ -65943,12 +65943,12 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/eth3d/exhibition_hall/images/scen_2/DSC_1782.JPG</t>
+          <t>/home/kamil/dataset/eth3d/exhibition_hall/images/scen_2/DSC_1768.JPG</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>DSC_1782.JPG</t>
+          <t>DSC_1768.JPG</t>
         </is>
       </c>
     </row>
@@ -70063,12 +70063,12 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/nerf_llff_data/fern/images/scen_1/IMG_4026.JPG</t>
+          <t>/home/kamil/dataset/nerf_llff_data/fern/images/scen_1/IMG_4029.JPG</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>IMG_4026.JPG</t>
+          <t>IMG_4029.JPG</t>
         </is>
       </c>
     </row>
@@ -74866,7 +74866,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10T17:07:56+00:00</t>
+          <t>2026-08-17T10:03:42+00:00</t>
         </is>
       </c>
     </row>
